--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC5A118-C671-45ED-B602-A029589D4049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBEAB16-9619-48AC-8F44-CB9AE6A7A0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,6 +205,15 @@
   </si>
   <si>
     <t>Felt very tired after continuous evening classes and I also skipped lunch because of it</t>
+  </si>
+  <si>
+    <t>Huirongbam Sania Devi</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
 </sst>
 </file>
@@ -891,26 +900,34 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12614602</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>57</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>58</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBEAB16-9619-48AC-8F44-CB9AE6A7A0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC225F9-E38A-46BD-B19F-F56D7A7C9BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -204,9 +204,6 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>Felt very tired after continuous evening classes and I also skipped lunch because of it</t>
-  </si>
-  <si>
     <t>Huirongbam Sania Devi</t>
   </si>
   <si>
@@ -214,6 +211,12 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>Felt very tired after consecutive evening classes and I even skipped lunch because of them</t>
+  </si>
+  <si>
+    <t>Busy day with classes and studying. Felt neural but consistent, and attentded all the 7 classes.</t>
   </si>
 </sst>
 </file>
@@ -901,7 +904,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -918,7 +921,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -926,7 +929,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1052,7 +1055,7 @@
         <v>240</v>
       </c>
       <c r="E7" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7" s="14">
         <v>250</v>
@@ -1065,11 +1068,11 @@
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1090</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>54</v>
@@ -1081,30 +1084,54 @@
         <v>51</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>450</v>
+      </c>
+      <c r="C8" s="14">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14">
+        <v>240</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>350</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>150</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC225F9-E38A-46BD-B19F-F56D7A7C9BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD6FB40-983E-4560-BCBE-F21AFD671B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>Busy day with classes and studying. Felt neural but consistent, and attentded all the 7 classes.</t>
+  </si>
+  <si>
+    <t>Honestly ,it was a pretty smooth day. Need to keep this momentum going.</t>
   </si>
 </sst>
 </file>
@@ -1133,27 +1136,51 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="14">
+        <v>500</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>270</v>
+      </c>
+      <c r="E9" s="14">
+        <v>100</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD6FB40-983E-4560-BCBE-F21AFD671B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5018C785-6C64-4A6F-9214-567DFB128909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1183,47 +1183,91 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B10" s="14">
+        <v>550</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>200</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B11" s="14">
+        <v>540</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>350</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>240</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
